--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,25 +923,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Expert, Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da5e0407b8df156</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3fe0d680994e3e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
+          <t>https://www.indeed.com/viewjob?jk=8da5e0407b8df156</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Modeler</t>
+          <t>Data Engineer + Gen AI (In-Person @ NYC)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nucleusteq</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>Glue, Google Cloud Platform, Dataflow, Cloud Storage, Hive, Spark, PySpark, Scala, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
+          <t>https://www.indeed.com/viewjob?jk=32f5af10a0a7af6f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP API Solution Architect</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653da5ce67465bb9</t>
+          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Modeler</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP API Solution Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=653da5ce67465bb9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53af07e478e3cd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Java/Python Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Columbia Threadneedle Investments</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
+          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Java/Python Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Columbia Threadneedle Investments</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
+          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
+          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer Core Infrastructure</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JetBlue</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
+          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GCP Associate Data Engineer</t>
+          <t>Senior Engineer Core Infrastructure</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JetBlue</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
+          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>GCP Associate Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
+          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Kubernetes)</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior DevOps Engineer (Kubernetes)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
+          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineer, Data</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
+          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer, Data</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Ensemble Health Partners</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sono Bello</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sono Bello</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
+          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior GCP API Data Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
+          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
+          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
         </is>
       </c>
     </row>
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=767b32d92360e6ef</t>
+          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60655539a4865f8d</t>
+          <t>https://www.indeed.com/viewjob?jk=767b32d92360e6ef</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
+          <t>https://www.indeed.com/viewjob?jk=60655539a4865f8d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
+          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Consultant - Remote</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
+          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Remote / Contract)</t>
+          <t>Sr. Data Engineering Consultant - Remote</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
+          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Senior Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Britecap Financial</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8192bd289c2151d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
+          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Britecap Financial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
+          <t>https://www.indeed.com/viewjob?jk=d8192bd289c2151d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Azure Databrick with Anaplan</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
+          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
+          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kubernetes Administrator</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Kubernetes Administrator</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Vanco</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52710d4b139f54d9</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
+          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AWS Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfaf9670e6dc175</t>
+          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ad8b697f6dd69d</t>
+          <t>https://www.indeed.com/viewjob?jk=acfaf9670e6dc175</t>
         </is>
       </c>
     </row>
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd7fe7b57ec9369c</t>
+          <t>https://www.indeed.com/viewjob?jk=28ad8b697f6dd69d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>US-Senior Software Engineer</t>
+          <t>AWS Data Scientist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd7fe7b57ec9369c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>US-Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Health in Tech</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Health in Tech</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
+          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - APIs</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, Spark Streaming, Kafka, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecb5dd3a0318428a</t>
+          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QA Engineer II - Marketing</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>QA Engineer II - Marketing</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
+          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Burnsville, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
+          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Richfield, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
+          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Richfield, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
         </is>
       </c>
     </row>
@@ -3343,12 +3343,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
+          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
+          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior SRE (Kubernetes)</t>
+          <t>Generative AI Intern</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior SRE (Kubernetes)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,17 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd5d72a84ca4e4ea</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
@@ -3793,17 +3793,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
+          <t>Database Engineer (Information Systems Specialist 7)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
+          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Luminate</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Luminate</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
+          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
+          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Google Cloud Solution Architect</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773d002c54ccd354</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Google Cloud Solution Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f2dcfd4ebf8840</t>
+          <t>https://www.indeed.com/viewjob?jk=0d854843d3afae2f</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, ETL, Tableau, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52708fba9fc5a109</t>
+          <t>https://www.indeed.com/viewjob?jk=02d0537fa0a4653f</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,14 +4871,14 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
+          <t>https://www.indeed.com/viewjob?jk=79249e7989055f0c</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Google Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=773d002c54ccd354</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - SRE</t>
+          <t>Google Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+          <t>https://www.indeed.com/viewjob?jk=01f2dcfd4ebf8840</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Azure Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Busigence Technologies</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
+          <t>Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, ETL, Tableau, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
+          <t>https://www.indeed.com/viewjob?jk=52708fba9fc5a109</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Verity Transcend</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Senior Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,67 +5046,67 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Busigence Technologies</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
+          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
+          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>Verity Transcend</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
+          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Machine Learning Test Capability Eng.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>GT Data Engineer II</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,34 +5246,34 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
+          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
+          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer (Analytics)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Rocket 55</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=450a9e8397744651</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Databricks Lakehouse, ETL</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30a75c1c6a28610f</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
+          <t>GT Data Engineer II</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Apply Digital</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>V&amp;V Engineer - AI-Driven Testing &amp; Validation</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30492497a365f912</t>
+          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>UX Software Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
+          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MTS Software Development Engineer</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
+          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Senior Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cascadia Services</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
+          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Sr Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Augustine Institute</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Florissant, MO, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Scala, ETL, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ebde076d2f48a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c63211f8f4eb21ae</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ApolloMD</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
+          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Junior Backend Developer</t>
+          <t>V&amp;V Engineer - AI-Driven Testing &amp; Validation</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
+          <t>https://www.indeed.com/viewjob?jk=30492497a365f912</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>MTS Software Development Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,17 +5736,192 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Application Developer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ApolloMD</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Junior Backend Developer</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Los Angeles Apparel</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>NiyamIT</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Machine Learning Intern</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>UX Software Engineer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Charles River Analytics</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior DevOps Engineer (Kubernetes)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zone 5 Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
+          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Kubernetes)</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Zone 5 Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
+          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Radus Software</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Google Cloud Platform, Scala, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=767b32d92360e6ef</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05b6965d015678</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1931,14 +1931,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60655539a4865f8d</t>
+          <t>https://www.indeed.com/viewjob?jk=767b32d92360e6ef</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
+          <t>https://www.indeed.com/viewjob?jk=60655539a4865f8d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
+          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Consultant - Remote</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
+          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineering Consultant - Remote</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
+          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Remote / Contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
+          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Senior Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
         </is>
       </c>
     </row>
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,29 +2271,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Britecap Financial</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8192bd289c2151d</t>
+          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Britecap Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
+          <t>https://www.indeed.com/viewjob?jk=d8192bd289c2151d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
+          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Azure Databrick with Anaplan</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
+          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kubernetes Administrator</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Kubernetes Administrator</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
+          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AWS Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfaf9670e6dc175</t>
+          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ad8b697f6dd69d</t>
+          <t>https://www.indeed.com/viewjob?jk=acfaf9670e6dc175</t>
         </is>
       </c>
     </row>
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd7fe7b57ec9369c</t>
+          <t>https://www.indeed.com/viewjob?jk=28ad8b697f6dd69d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>US-Senior Software Engineer</t>
+          <t>AWS Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd7fe7b57ec9369c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>US-Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Health in Tech</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Health in Tech</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
+          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
         </is>
       </c>
     </row>
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
+          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QA Engineer II - Marketing</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>Spokeo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, EMR, S3, RDS, Dataflow, Spark, PySpark, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
+          <t>https://www.indeed.com/viewjob?jk=e67ac700a108f786</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>QA Engineer II - Marketing</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
+          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
+          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Burnsville, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
+          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richfield, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
         </is>
       </c>
     </row>
@@ -3378,12 +3378,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Richfield, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
+          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior SRE (Kubernetes)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
+          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Generative AI Intern</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior SRE (Kubernetes)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Power BI Developer - Freelance</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Reapplix</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer / Senior Data Engineer</t>
+          <t>Power BI Developer - Freelance</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Reapplix</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
+          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer / Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Database Engineer (Information Systems Specialist 7)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Luminate</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
+          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Luminate</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
+          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Fractional/Part-Time CTO</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Performacentric</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d854843d3afae2f</t>
+          <t>https://www.indeed.com/viewjob?jk=668daa117d5cd90c</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Fractional CTO- Chicago</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Performacentric</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d0537fa0a4653f</t>
+          <t>https://www.indeed.com/viewjob?jk=bbb61f67fa9a3b09</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79249e7989055f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Google Cloud Solution Architect</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773d002c54ccd354</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Google Cloud Solution Architect</t>
+          <t>Fractional/Part-Time CTO</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Performacentric</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f2dcfd4ebf8840</t>
+          <t>https://www.indeed.com/viewjob?jk=18922cc00f47c2b7</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,34 +4966,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, ETL, Tableau, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52708fba9fc5a109</t>
+          <t>https://www.indeed.com/viewjob?jk=0d854843d3afae2f</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=02d0537fa0a4653f</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - SRE</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+          <t>https://www.indeed.com/viewjob?jk=79249e7989055f0c</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Google Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Busigence Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
+          <t>https://www.indeed.com/viewjob?jk=773d002c54ccd354</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Google Cloud Solution Architect</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
+          <t>https://www.indeed.com/viewjob?jk=01f2dcfd4ebf8840</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>Azure Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Verity Transcend</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, ETL, Tableau, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
+          <t>https://www.indeed.com/viewjob?jk=52708fba9fc5a109</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Machine Learning Test Capability Eng.</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Senior Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,67 +5221,67 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Busigence Technologies</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
+          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
+          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>Verity Transcend</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,59 +5326,59 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
+          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Engineer III, SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
+          <t>https://www.indeed.com/viewjob?jk=6baf774b1b56a4a3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Machine Learning Test Capability Eng.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GT Data Engineer II</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
+          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
+          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Software Engineer III-ETL/PySpark</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Cascadia Services</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Eagle, ID, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,34 +5596,34 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Backend</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Augustine Institute</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Florissant, MO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Scala, ETL, ELT, Kubernetes</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c63211f8f4eb21ae</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
+          <t>GT Data Engineer II</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Apply Digital</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>V&amp;V Engineer - AI-Driven Testing &amp; Validation</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30492497a365f912</t>
+          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>MTS Software Development Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
+          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Software Engineer III-ETL/PySpark</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ApolloMD</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
+          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Junior Backend Developer</t>
+          <t>Senior Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Cascadia Services</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
+          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr Software Engineer - Backend</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NiyamIT</t>
+          <t>Augustine Institute</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Florissant, MO, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Scala, ETL, ELT, Kubernetes</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
+          <t>https://www.indeed.com/viewjob?jk=c63211f8f4eb21ae</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
+          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>UX Software Engineer</t>
+          <t>V&amp;V Engineer - AI-Driven Testing &amp; Validation</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,17 +5911,227 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30492497a365f912</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>UX Software Engineer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Charles River Analytics</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>MTS Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Machine Learning Intern</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Senior Application Developer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ApolloMD</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Junior Backend Developer</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Los Angeles Apparel</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>NiyamIT</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G163"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Expert, Cloud Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Snowflake, Oracle</t>
+          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3fe0d680994e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=66a4800f2fbccdc3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Data Engineer, Mortgage Servicing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da5e0407b8df156</t>
+          <t>https://www.indeed.com/viewjob?jk=75c41866a1b74cb7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer + Gen AI (In-Person @ NYC)</t>
+          <t>Expert, Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nucleusteq</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glue, Google Cloud Platform, Dataflow, Cloud Storage, Hive, Spark, PySpark, Scala, MySQL, NoSQL</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f5af10a0a7af6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3fe0d680994e3e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
+          <t>https://www.indeed.com/viewjob?jk=8da5e0407b8df156</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Modeler</t>
+          <t>Data Engineer + Gen AI (In-Person @ NYC)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nucleusteq</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>Glue, Google Cloud Platform, Dataflow, Cloud Storage, Hive, Spark, PySpark, Scala, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
+          <t>https://www.indeed.com/viewjob?jk=32f5af10a0a7af6f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP API Solution Architect</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653da5ce67465bb9</t>
+          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - AWS Glue / Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=093ec4d8db7a7a45</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Modeler</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Java/Python Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Columbia Threadneedle Investments</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
+          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Scala, Snowflake, Oracle, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39123815bfb490a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Java/Python Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Columbia Threadneedle Investments</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer Core Infrastructure</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JetBlue</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
+          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GCP Associate Data Engineer</t>
+          <t>Senior Engineer Core Infrastructure</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JetBlue</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
+          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>GCP Associate Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
+          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Kubernetes)</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior DevOps Engineer (Kubernetes)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
+          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineer, Data</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
+          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer, Data</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Ensemble Health Partners</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sono Bello</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>National Council on Aging</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
+          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sono Bello</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
+          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior GCP API Data Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
         </is>
       </c>
     </row>
@@ -1791,14 +1791,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
+          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
         </is>
       </c>
     </row>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Radus Software</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Google Cloud Platform, Scala, Oracle, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,14 +1896,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05b6965d015678</t>
+          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=767b32d92360e6ef</t>
+          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Radus Software</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Google Cloud Platform, Scala, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60655539a4865f8d</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05b6965d015678</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Britecap Financial</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8192bd289c2151d</t>
+          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Azure Databrick with Anaplan</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
+          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Kubernetes Administrator</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kubernetes Administrator</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
+          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>US-Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Data Scientist</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Health in Tech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfaf9670e6dc175</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AWS Data Scientist</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ad8b697f6dd69d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS Data Scientist</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, RDS, Spark, Scala, MLOps</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd7fe7b57ec9369c</t>
+          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>US-Senior Software Engineer</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Health in Tech</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
+          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>QA Engineer II - Marketing</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
+          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
+          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Spokeo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Dataflow, Spark, PySpark, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67ac700a108f786</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>QA Engineer II - Marketing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,17 +3076,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
+          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Burnsville, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>Richfield, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
+          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
+          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Generative AI Intern</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior SRE (Kubernetes)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Richfield, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior SRE (Kubernetes)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
+          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Power BI Developer - Freelance</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Reapplix</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Consertus</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer / Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,67 +3681,67 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Machine Learning Engineer - Healthcare</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>MD Anderson Cancer Center</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
+          <t>https://www.indeed.com/viewjob?jk=589534468e92c6da</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Power BI Developer - Freelance</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Reapplix</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer / Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Database Engineer (Information Systems Specialist 7)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,19 +4486,19 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Luminate</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
+          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
+          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Luminate</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
+          <t>Senior Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Fractional/Part-Time CTO</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Performacentric</t>
+          <t>Busigence Technologies</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=668daa117d5cd90c</t>
+          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Fractional CTO- Chicago</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Performacentric</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbb61f67fa9a3b09</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
+          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>Verity Transcend</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,137 +4906,137 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Fractional/Part-Time CTO</t>
+          <t>Machine Learning Test Capability Eng.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Performacentric</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18922cc00f47c2b7</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d854843d3afae2f</t>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, Azure, DynamoDB, CI/CD</t>
+          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d0537fa0a4653f</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Oracle, NoSQL, Data Modeling, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79249e7989055f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Google Cloud Solution Architect</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=773d002c54ccd354</t>
+          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Google Cloud Solution Architect</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f2dcfd4ebf8840</t>
+          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Azure Databricks Senior Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Hadoop, Hive, Spark, PySpark, ETL, Tableau, Kubernetes</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52708fba9fc5a109</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - SRE</t>
+          <t>GT Data Engineer II</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,67 +5221,67 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Busigence Technologies</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,94 +5291,94 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
+          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>Senior Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Verity Transcend</t>
+          <t>Cascadia Services</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
+          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Engineer III, SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>MTS Software Development Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6baf774b1b56a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Machine Learning Test Capability Eng.</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>ApolloMD</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
+          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>Junior Backend Developer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>NiyamIT</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
+          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,567 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Tiger Analytics</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>GT Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Kubernetes Security Engineer</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Software Engineer III-ETL/PySpark</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, dbt, CI/CD, Airflow</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2032a94f0b2c0e2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer/Architect</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Cascadia Services</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Eagle, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer - Backend</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Augustine Institute</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Florissant, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Scala, ETL, ELT, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c63211f8f4eb21ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Apply Digital</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>V&amp;V Engineer - AI-Driven Testing &amp; Validation</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30492497a365f912</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>UX Software Engineer</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Charles River Analytics</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>MTS Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Machine Learning Intern</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Senior Application Developer</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>ApolloMD</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Junior Backend Developer</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>NiyamIT</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>US Pharmacopeial Convention</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SNS, IAM</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3903be92908c75d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f94ba7cfeb5a99</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Architect with 15 year's experience local to Chicago</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>US Pharmacopeial Convention</t>
+          <t>Sanford AI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.9</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
+          <t>IAM, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f94ba7cfeb5a99</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb6ec77e71bc3c8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Kubernetes Cloud Engineer (EKS)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Azure, Hadoop</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Vertex AI, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fe8958cd4a14a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4556ba273a002c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GCP Data Architect with 15 year's experience local to Chicago</t>
+          <t>Cloud Operations Associate (GCP)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sanford AI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IAM, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb6ec77e71bc3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b1c67caa8dada84</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Junior Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Vertex AI, Hive, Spark, PySpark</t>
+          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4556ba273a002c</t>
+          <t>https://www.indeed.com/viewjob?jk=1272708dac2e408f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Operations Associate (GCP)</t>
+          <t>DHCF Azure Data Solutions Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Collaboredge</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b1c67caa8dada84</t>
+          <t>https://www.indeed.com/viewjob?jk=cf5e6b653bcbed06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Junior Kubernetes Engineer</t>
+          <t>Azure Data Solutions Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gointellects Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1272708dac2e408f</t>
+          <t>https://www.indeed.com/viewjob?jk=413624100870427f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DHCF Azure Data Solutions Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Collaboredge</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf5e6b653bcbed06</t>
+          <t>https://www.indeed.com/viewjob?jk=f631622e574168df</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azure Data Solutions Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gointellects Inc.</t>
+          <t>Cadrac Labs India Private Limited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Texas City, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413624100870427f</t>
+          <t>https://www.indeed.com/viewjob?jk=747aafe9f6bd6536</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Spark</t>
+          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f631622e574168df</t>
+          <t>https://www.indeed.com/viewjob?jk=66a4800f2fbccdc3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer, Mortgage Servicing</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cadrac Labs India Private Limited</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Texas City, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747aafe9f6bd6536</t>
+          <t>https://www.indeed.com/viewjob?jk=75c41866a1b74cb7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Expert, Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a4800f2fbccdc3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3fe0d680994e3e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer, Mortgage Servicing</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c41866a1b74cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=8da5e0407b8df156</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Expert, Cloud Database Engineer</t>
+          <t>Data Engineer + Gen AI (In-Person @ NYC)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Nucleusteq</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Snowflake, Oracle</t>
+          <t>Glue, Google Cloud Platform, Dataflow, Cloud Storage, Hive, Spark, PySpark, Scala, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3fe0d680994e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=32f5af10a0a7af6f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da5e0407b8df156</t>
+          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer + Gen AI (In-Person @ NYC)</t>
+          <t>Software Engineer III - AWS Glue / Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nucleusteq</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glue, Google Cloud Platform, Dataflow, Cloud Storage, Hive, Spark, PySpark, Scala, MySQL, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f5af10a0a7af6f</t>
+          <t>https://www.indeed.com/viewjob?jk=093ec4d8db7a7a45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Senior Data Modeler</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
+          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue / Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=093ec4d8db7a7a45</t>
+          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Modeler</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
+          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java/Python Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>Columbia Threadneedle Investments</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Java/Python Senior Software Engineer</t>
+          <t>Senior Engineer Core Infrastructure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Columbia Threadneedle Investments</t>
+          <t>JetBlue</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
+          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>GCP Associate Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer Core Infrastructure</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JetBlue</t>
+          <t>Zone 5 Technologies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
+          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GCP Associate Data Engineer</t>
+          <t>Senior DevOps Engineer (Kubernetes)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
+          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Engineer, Data</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ensemble Health Partners</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, Azure, Google Cloud Platform, Oracle, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0077323c8678a550</t>
+          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zone 5 Technologies</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Kubernetes)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>National Council on Aging</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, SNS, RDS, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c43b6c07f7a10c25</t>
+          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>Sono Bello</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
+          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>National Council on Aging</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
+          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sono Bello</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
+          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
         </is>
       </c>
     </row>
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
+          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior GCP API Data Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Radus Software</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Google Cloud Platform, Scala, Oracle, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=fb05b6965d015678</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
+          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Radus Software</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Google Cloud Platform, Scala, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05b6965d015678</t>
+          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Sr. Data Engineering Consultant - Remote</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
+          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
+          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Consultant - Remote</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
+          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Remote / Contract)</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
+          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
+          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
+          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Kubernetes Administrator</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Azure Databrick with Anaplan</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
+          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>US-Senior Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Health in Tech</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kubernetes Administrator</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d7d81277bb81ba</t>
+          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
+          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>US-Senior Software Engineer</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Health in Tech</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>QA Engineer II - Marketing</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
+          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QA Engineer II - Marketing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
+          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Burnsville, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>Richfield, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
+          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
         </is>
       </c>
     </row>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
+          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Generative AI Intern</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
+          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Power BI Developer - Freelance</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Reapplix</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richfield, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
+          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior SRE (Kubernetes)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2d3d34de1eead8b</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer / Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,67 +3436,67 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Machine Learning Engineer - Healthcare</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>MD Anderson Cancer Center</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=589534468e92c6da</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Power BI Developer - Freelance</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Reapplix</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Consertus</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8919022f4b2c0bc4</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer / Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Healthcare</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MD Anderson Cancer Center</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589534468e92c6da</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Database Engineer (Information Systems Specialist 7)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Luminate</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,14 +4451,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Senior Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Luminate</t>
+          <t>Busigence Technologies</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
+          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Containers &amp; Kubernetes)</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Verity Transcend</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, Oracle, DynamoDB, ETL, CI/CD, Jenkins, Terraform</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=472d3fada936445a</t>
+          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Machine Learning Test Capability Eng.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
+          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,67 +4696,67 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - SRE</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,67 +4766,67 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Busigence Technologies</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
+          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
+          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Verity Transcend</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Machine Learning Test Capability Eng.</t>
+          <t>GT Data Engineer II</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
+          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>MTS Software Development Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>ApolloMD</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
+          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Junior Backend Developer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Cascadia Services</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
+          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
+          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>GT Data Engineer II</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5255,321 +5255,6 @@
         </is>
       </c>
       <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Kubernetes Security Engineer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer/Architect</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Cascadia Services</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Eagle, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>MTS Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Apply Digital</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Machine Learning Intern</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Senior Application Developer</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>ApolloMD</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Junior Backend Developer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>NiyamIT</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MySQL, ETL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb8eb5661e9cdc17</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>UX Software Engineer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Charles River Analytics</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
         </is>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
@@ -3163,17 +3163,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Power BI Developer - Freelance</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Reapplix</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Power BI Developer - Freelance</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Reapplix</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
+          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
         </is>
       </c>
     </row>
@@ -4353,17 +4353,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - SRE</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Busigence Technologies</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Busigence Technologies</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,17 +4546,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
+          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
+          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
+          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>GT Data Engineer II</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
+          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MTS Software Development Engineer</t>
+          <t>GT Data Engineer II</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ApolloMD</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
+          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Junior Backend Developer</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
+          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
         </is>
       </c>
     </row>
@@ -5158,17 +5158,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
+          <t>MTS Software Development Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Apply Digital</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
+          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>UX Software Engineer</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,15 +5246,120 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Senior Application Developer</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>ApolloMD</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Junior Backend Developer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Los Angeles Apparel</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>UX Software Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Charles River Analytics</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
         </is>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
+          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Healthcare</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MD Anderson Cancer Center</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589534468e92c6da</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Database Engineer (Information Systems Specialist 7)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Luminate</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Luminate</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
+          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Senior Machine Learning Engineer - Healthcare</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MD Anderson Cancer Center</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,17 +4336,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=589534468e92c6da</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Radus Software</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Google Cloud Platform, Scala, Oracle, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb05b6965d015678</t>
+          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
+          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Sr. Data Engineering Consultant - Remote</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
+          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Consultant - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
+          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Remote / Contract)</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
         </is>
       </c>
     </row>
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
+          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
+          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Azure Databrick with Anaplan</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
+          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Kubernetes Administrator</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kubernetes Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>US-Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>US-Senior Software Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Health in Tech</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Health in Tech</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
+          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
         </is>
       </c>
     </row>
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
+          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>QA Engineer II - Marketing</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QA Engineer II - Marketing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
+          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
+          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Burnsville, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
+          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
+          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Richfield, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richfield, MN, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Generative AI Intern</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
+          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Power BI Developer - Freelance</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Reapplix</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
+          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Power BI Developer - Freelance</t>
+          <t>Data Engineer / Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Reapplix</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer / Senior Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Database Engineer (Information Systems Specialist 7)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Luminate</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Luminate</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
+          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Senior Machine Learning Engineer - Healthcare</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MD Anderson Cancer Center</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=589534468e92c6da</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Healthcare</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>MD Anderson Cancer Center</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589534468e92c6da</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - SRE</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Busigence Technologies</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Busigence Technologies</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
+          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Verity Transcend</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,32 +4591,32 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
+          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>Machine Learning Test Capability Eng.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Verity Transcend</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Machine Learning Test Capability Eng.</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
+          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>GT Data Engineer II</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
+          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
+          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>GT Data Engineer II</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
+          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
+          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>Senior Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cascadia Services</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
+          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Architect</t>
+          <t>MTS Software Development Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cascadia Services</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Eagle, ID, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,34 +5141,34 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MTS Software Development Engineer</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
+          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Apply Digital</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Machine Learning Intern</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
+          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
         </is>
       </c>
     </row>
@@ -5327,41 +5327,6 @@
       <c r="G140" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>UX Software Engineer</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Charles River Analytics</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Senior Data Engineer - AI and Analytics</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
+          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Consultant - Remote</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
+          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineering Consultant - Remote</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
+          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Remote / Contract)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
+          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Senior Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
         </is>
       </c>
     </row>
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2646dabbd2b10</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,42 +2131,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=482024a3058d442e</t>
+          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,14 +2211,14 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Azure Databrick with Anaplan</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
+          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Kubernetes Administrator</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kubernetes Administrator</t>
+          <t>US-Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Health in Tech</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, RDS, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05116eeafaa39819</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>US-Senior Software Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Health in Tech</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
+          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
+          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>QA Engineer II - Marketing</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>QA Engineer II - Marketing</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>Burnsville, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
+          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
+          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Richfield, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
+          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
         </is>
       </c>
     </row>
@@ -2993,12 +2993,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Richfield, MN, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
+          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Generative AI Intern</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer / Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Power BI Developer - Freelance</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Reapplix</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99bc276d95bde95</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer / Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Database Engineer (Information Systems Specialist 7)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
+          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>Luminate</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Luminate</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer - Healthcare</t>
+          <t>Senior Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MD Anderson Cancer Center</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=589534468e92c6da</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Verity Transcend</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,19 +4416,19 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - SRE</t>
+          <t>Machine Learning Test Capability Eng.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4437,11 +4437,11 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,102 +4451,102 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Busigence Technologies</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, API Gateway, RDS, Azure, GCP, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30186b8478a082ea</t>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Verity Transcend</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
+          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Machine Learning Test Capability Eng.</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
+          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>GT Data Engineer II</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
+          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
+          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
+          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GT Data Engineer II</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
+          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>Cascadia Services</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
+          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Kubernetes Security Engineer</t>
+          <t>MTS Software Development Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,34 +5001,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,34 +5036,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ApolloMD</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,34 +5071,34 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Architect</t>
+          <t>Junior Backend Developer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Cascadia Services</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Eagle, ID, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,34 +5106,34 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MTS Software Development Engineer</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,182 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Apply Digital</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Machine Learning Intern</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>UX Software Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Charles River Analytics</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior Application Developer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>ApolloMD</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Junior Backend Developer</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G135"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Data Architect with 15 year's experience local to Chicago</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>US Pharmacopeial Convention</t>
+          <t>Sanford AI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.9</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
+          <t>IAM, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f94ba7cfeb5a99</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb6ec77e71bc3c8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP Data Architect with 15 year's experience local to Chicago</t>
+          <t>DHCF Azure Data Solutions Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sanford AI</t>
+          <t>Collaboredge</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb6ec77e71bc3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=cf5e6b653bcbed06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kubernetes Cloud Engineer (EKS)</t>
+          <t>Azure Data Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gointellects Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, RDS, Vertex AI, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4556ba273a002c</t>
+          <t>https://www.indeed.com/viewjob?jk=413624100870427f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Operations Associate (GCP)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, GCP</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b1c67caa8dada84</t>
+          <t>https://www.indeed.com/viewjob?jk=f631622e574168df</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Junior Kubernetes Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cadrac Labs India Private Limited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Texas City, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, ECS, IAM, RDS, Azure, Google Cloud Platform, Oracle</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1272708dac2e408f</t>
+          <t>https://www.indeed.com/viewjob?jk=747aafe9f6bd6536</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DHCF Azure Data Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Collaboredge</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf5e6b653bcbed06</t>
+          <t>https://www.indeed.com/viewjob?jk=66a4800f2fbccdc3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Azure Data Solutions Architect</t>
+          <t>Data Engineer, Mortgage Servicing</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gointellects Inc.</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413624100870427f</t>
+          <t>https://www.indeed.com/viewjob?jk=75c41866a1b74cb7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Expert, Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Spark</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f631622e574168df</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3fe0d680994e3e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cadrac Labs India Private Limited</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Texas City, IL, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747aafe9f6bd6536</t>
+          <t>https://www.indeed.com/viewjob?jk=8da5e0407b8df156</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer + Gen AI (In-Person @ NYC)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Nucleusteq</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,81 +867,81 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>Glue, Google Cloud Platform, Dataflow, Cloud Storage, Hive, Spark, PySpark, Scala, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a4800f2fbccdc3</t>
+          <t>https://www.indeed.com/viewjob?jk=32f5af10a0a7af6f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer, Mortgage Servicing</t>
+          <t>Software Engineer III - AWS Glue / Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c41866a1b74cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=093ec4d8db7a7a45</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Expert, Cloud Database Engineer</t>
+          <t>Senior Data Modeler</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Snowflake, Oracle</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3fe0d680994e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da5e0407b8df156</t>
+          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer + Gen AI (In-Person @ NYC)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nucleusteq</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glue, Google Cloud Platform, Dataflow, Cloud Storage, Hive, Spark, PySpark, Scala, MySQL, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f5af10a0a7af6f</t>
+          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Java/Python Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Columbia Threadneedle Investments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d816abd278fc697</t>
+          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue / Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=093ec4d8db7a7a45</t>
+          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Modeler</t>
+          <t>Senior Engineer Core Infrastructure</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JetBlue</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
+          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Associate Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Zone 5 Technologies</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Java/Python Senior Software Engineer</t>
+          <t>Engineer, Data</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Columbia Threadneedle Investments</t>
+          <t>Ensemble Health Partners</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
+          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer Core Infrastructure</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JetBlue</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GCP Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>National Council on Aging</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
+          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Zone 5 Technologies</t>
+          <t>Sono Bello</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
+          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Kubernetes)</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Scala, Kafka, NoSQL, MLOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381d7c89737513ad</t>
+          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineer, Data</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>National Council on Aging</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sono Bello</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
+          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
+          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior GCP API Data Engineer</t>
+          <t>Senior Data Engineer - AI and Analytics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
+          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Sr. Data Engineering Consultant - Remote</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
+          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,19 +1791,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1812,11 +1812,11 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior Platform Engineer (Azure)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>Blue Sentry Cloud</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1847,11 +1847,11 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a8fd660470fa589</t>
+          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI and Analytics</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
+          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Consultant - Remote</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,14 +2001,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
+          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2018,15 +2018,15 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
+          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Remote / Contract)</t>
+          <t>US-Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>Health in Tech</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
+          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
+          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Azure Databrick with Anaplan</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
+          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>QA Engineer II - Marketing</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
+          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kubernetes Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage, MySQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6b8298e9c03f5f</t>
+          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>US-Senior Software Engineer</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Health in Tech</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
+          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Burnsville, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
+          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03cd36eaa85418b7</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9632e09bbc8fbcf</t>
+          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Richfield, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>QA Engineer II - Marketing</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Sonar</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
+          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer / Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Richfield, MN, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Generative AI Intern</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Google Cloud Platform, BigQuery, Vertex AI, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be60fbee58aedc1</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer / Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Database Engineer (Information Systems Specialist 7)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,19 +3786,19 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Verity Transcend</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
+          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Machine Learning Test Capability Eng.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,67 +4031,67 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineering Intern, DataOps Engineering / Data Engineering</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Luminate</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Snowflake, dbt, DataOps, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e13b4073216a84</t>
+          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a800b3931c11c7a</t>
+          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>GT Data Engineer II</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - SRE</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,129 +4311,129 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
+          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Verity Transcend</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
+          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Machine Learning Test Capability Eng.</t>
+          <t>Senior Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Cascadia Services</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,29 +4441,29 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>MTS Software Development Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
+          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
+          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>ApolloMD</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
+          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Junior Backend Developer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,532 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Tiger Analytics</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>GT Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Kubernetes Security Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88f3624dd7e6a601</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer/Architect</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Cascadia Services</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Eagle, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>MTS Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Apply Digital</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Machine Learning Intern</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca7c2d316ed79d27</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Application Developer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>ApolloMD</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Junior Backend Developer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>UX Software Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Charles River Analytics</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cadrac Labs India Private Limited</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Texas City, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,14 +706,14 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747aafe9f6bd6536</t>
+          <t>https://www.indeed.com/viewjob?jk=66a4800f2fbccdc3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Mortgage Servicing</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a4800f2fbccdc3</t>
+          <t>https://www.indeed.com/viewjob?jk=75c41866a1b74cb7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer, Mortgage Servicing</t>
+          <t>Expert, Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c41866a1b74cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3fe0d680994e3e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Expert, Cloud Database Engineer</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3fe0d680994e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8da5e0407b8df156</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Data Engineer + Gen AI (In-Person @ NYC)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nucleusteq</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>Glue, Google Cloud Platform, Dataflow, Cloud Storage, Hive, Spark, PySpark, Scala, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da5e0407b8df156</t>
+          <t>https://www.indeed.com/viewjob?jk=32f5af10a0a7af6f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer + Gen AI (In-Person @ NYC)</t>
+          <t>Software Engineer III - AWS Glue / Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Nucleusteq</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Glue, Google Cloud Platform, Dataflow, Cloud Storage, Hive, Spark, PySpark, Scala, MySQL, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f5af10a0a7af6f</t>
+          <t>https://www.indeed.com/viewjob?jk=093ec4d8db7a7a45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue / Data Engineer</t>
+          <t>Senior Data Modeler</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=093ec4d8db7a7a45</t>
+          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Modeler</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java/Python Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>Columbia Threadneedle Investments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java/Python Senior Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Columbia Threadneedle Investments</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
+          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Engineer Core Infrastructure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>JetBlue</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer Core Infrastructure</t>
+          <t>GCP Associate Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JetBlue</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
+          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP Associate Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Zone 5 Technologies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
+          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Engineer, Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Zone 5 Technologies</t>
+          <t>Ensemble Health Partners</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
+          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
+          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Hinge</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>National Council on Aging</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>National Council on Aging</t>
+          <t>Sono Bello</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sono Bello</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
+          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
+          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior GCP API Data Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
         </is>
       </c>
     </row>
@@ -1546,14 +1546,14 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
+          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior Data Engineer - AI and Analytics</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI and Analytics</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
+          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Sr. Data Engineering Consultant - Remote</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
+          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Consultant - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
+          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Remote / Contract)</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
+          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Azure)</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Sentry Cloud</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Scala, NoSQL, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad9db5da19a8799</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
+          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Azure Databrick with Anaplan</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
+          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>US-Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Health in Tech</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>US-Senior Software Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Sr Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Health in Tech</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Development Engineer in Test, ML</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
+          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,59 +2176,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>QA Engineer II - Marketing</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
+          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>QA Engineer II - Marketing</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>Burnsville, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
+          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
+          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Richfield, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
+          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richfield, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sonar</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>S3, BigQuery, Dataflow, Cloud Storage, SQL Server, MySQL, MongoDB, NoSQL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ccfeeca461865f</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer / Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer / Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Database Engineer (Information Systems Specialist 7)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - SRE</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Verity Transcend</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Machine Learning Test Capability Eng.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,59 +3926,59 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Verity Transcend</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Machine Learning Test Capability Eng.</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
+          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>GT Data Engineer II</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
+          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>GT Data Engineer II</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
+          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
+          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Cascadia Services</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>MTS Software Development Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Architect</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Cascadia Services</t>
+          <t>ApolloMD</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Eagle, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
+          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MTS Software Development Engineer</t>
+          <t>Junior Backend Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Apply Digital</t>
+          <t>Charles River Analytics</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,112 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>UX Software Engineer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Charles River Analytics</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Cambridge, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Application Developer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>ApolloMD</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Junior Backend Developer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GCP Data Architect with 15 year's experience local to Chicago</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sanford AI</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IAM, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb6ec77e71bc3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=9684b1e8c83efb55</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DHCF Azure Data Solutions Architect</t>
+          <t>GCP Data Architect with 15 year's experience local to Chicago</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Collaboredge</t>
+          <t>Sanford AI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>IAM, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf5e6b653bcbed06</t>
+          <t>https://www.indeed.com/viewjob?jk=fcb6ec77e71bc3c8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Azure Data Solutions Architect</t>
+          <t>DHCF Azure Data Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gointellects Inc.</t>
+          <t>Collaboredge</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=413624100870427f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf5e6b653bcbed06</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>Spokeo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, EMR, S3, RDS, Dataflow, Spark, PySpark, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=e67ac700a108f786</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QA Engineer II - Marketing</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>QA Engineer II - Marketing</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Tailored Brands</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
+          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Golden Valley, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Burnsville, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
+          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
+          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richfield, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
+          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Richfield, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
+          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer / Senior Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer / Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
+          <t>Database Engineer (Information Systems Specialist 7)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
+          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - SRE</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Senior Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Verity Transcend</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
+          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Machine Learning Test Capability Eng.</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Verity Transcend</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Machine Learning Test Capability Eng.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
+          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
+          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>GT Data Engineer II</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>GT Data Engineer II</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Simplot Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Simplot Company</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
+          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer/Architect</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cascadia Services</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Eagle, ID, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
+          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MTS Software Development Engineer</t>
+          <t>Senior Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Cascadia Services</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
+          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
+          <t>MTS Software Development Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Apply Digital</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ApolloMD</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
+          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Junior Backend Developer</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Los Angeles Apparel</t>
+          <t>ApolloMD</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
+          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>UX Software Engineer</t>
+          <t>Junior Backend Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Charles River Analytics</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, MySQL, MongoDB, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5392f87fadaec778</t>
+          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DHCF Azure Data Solutions Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Collaboredge</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf5e6b653bcbed06</t>
+          <t>https://www.indeed.com/viewjob?jk=f631622e574168df</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Spark</t>
+          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f631622e574168df</t>
+          <t>https://www.indeed.com/viewjob?jk=66a4800f2fbccdc3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Mortgage Servicing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a4800f2fbccdc3</t>
+          <t>https://www.indeed.com/viewjob?jk=75c41866a1b74cb7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer, Mortgage Servicing</t>
+          <t>Expert, Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c41866a1b74cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3fe0d680994e3e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Expert, Cloud Database Engineer</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3fe0d680994e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8da5e0407b8df156</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Data Engineer + Gen AI (In-Person @ NYC)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Nucleusteq</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,69 +801,69 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>Glue, Google Cloud Platform, Dataflow, Cloud Storage, Hive, Spark, PySpark, Scala, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da5e0407b8df156</t>
+          <t>https://www.indeed.com/viewjob?jk=32f5af10a0a7af6f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer + Gen AI (In-Person @ NYC)</t>
+          <t>Software Engineer III - AWS Glue / Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nucleusteq</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Glue, Google Cloud Platform, Dataflow, Cloud Storage, Hive, Spark, PySpark, Scala, MySQL, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f5af10a0a7af6f</t>
+          <t>https://www.indeed.com/viewjob?jk=093ec4d8db7a7a45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue / Data Engineer</t>
+          <t>Senior Data Modeler</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=093ec4d8db7a7a45</t>
+          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Modeler</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java/Python Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>Columbia Threadneedle Investments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CPI Security</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c114283168214bd2</t>
+          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java/Python Senior Software Engineer</t>
+          <t>Senior Engineer Core Infrastructure</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Columbia Threadneedle Investments</t>
+          <t>JetBlue</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
+          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>GCP Associate Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer Core Infrastructure</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JetBlue</t>
+          <t>Zone 5 Technologies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
+          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP Associate Data Engineer</t>
+          <t>Engineer, Data</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Ensemble Health Partners</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
+          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zone 5 Technologies</t>
+          <t>National Council on Aging</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
+          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>Sono Bello</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
+          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ascendion</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, Databricks, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03c0c824aa43ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hinge</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f8363856d6fd5ea</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>National Council on Aging</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
+          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sono Bello</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
+          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
         </is>
       </c>
     </row>
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
+          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior GCP API Data Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior Data Engineer - AI and Analytics</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
+          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Sr. Data Engineering Consultant - Remote</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
+          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI and Analytics</t>
+          <t>Senior Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Stony Brook University</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
+          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Consultant - Remote</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
+          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Remote / Contract)</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
+          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Senior Business Intelligence Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>US-Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>R1 RCM</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure Databrick with Anaplan</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
+          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Spokeo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, EMR, S3, RDS, Dataflow, Spark, PySpark, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=e67ac700a108f786</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>US-Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Health in Tech</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5057bd977bc6a4</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2053,15 +2053,15 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer in Test, ML</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65fb9eb3f94c2fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test, ML</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a9750053034f93</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Spokeo</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Dataflow, Spark, PySpark, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67ac700a108f786</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QA Engineer II - Marketing</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tailored Brands</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=311d3be688689336</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>Data Engineer / Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GreenStone Farm Credit Services</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>East Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
+          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Golden Valley, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c75e31192e70f299</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378ba0a224291a9</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Burnsville, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3454b8bb44e492ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f4be82e636b033</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61284841e88348e1</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richfield, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03781722277716e</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a4e8b14af6dcfdc</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer / Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Database Engineer (Information Systems Specialist 7)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Verity Transcend</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Machine Learning Test Capability Eng.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,67 +3436,67 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
+          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>GT Data Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,207 +3681,207 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>Sr. Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>Applix Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - SRE</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
+          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Cascadia Services</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
+          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>MTS Software Development Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Verity Transcend</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Machine Learning Test Capability Eng.</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>ApolloMD</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Junior Backend Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,540 +3986,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Senior Data Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Stanford Health Care</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Cloudelligent</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Cloudelligent</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Tiger Analytics</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>GT Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Engineer III</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Simplot Company</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8023652bf999f536</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer/Architect</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Cascadia Services</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Eagle, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>MTS Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Apply Digital</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Senior Application Developer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>ApolloMD</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Junior Backend Developer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
         </is>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,12 +923,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java/Python Senior Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Columbia Threadneedle Investments</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -937,11 +937,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Snowflake</t>
+          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96306aa5fb1c0b90</t>
+          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Engineer Core Infrastructure</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>JetBlue</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer Core Infrastructure</t>
+          <t>GCP Associate Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JetBlue</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
+          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP Associate Data Engineer</t>
+          <t>DevOps Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Zone 5 Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
+          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Engineer, Data</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zone 5 Technologies</t>
+          <t>Ensemble Health Partners</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
+          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Engineer, Data</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>National Council on Aging</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
+          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>National Council on Aging</t>
+          <t>Sono Bello</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sono Bello</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
+          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
+          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior GCP API Data Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
         </is>
       </c>
     </row>
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
+          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,59 +1441,59 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Senior Data Engineer - AI and Analytics</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI and Analytics</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
+          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Sr. Data Engineering Consultant - Remote</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
+          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Consultant - Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
+          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Remote / Contract)</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Stony Brook University</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=572f829e354bce2a</t>
+          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,14 +1721,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
+          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Azure Databrick with Anaplan</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
+          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Spokeo</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, EMR, S3, RDS, Dataflow, Spark, PySpark, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=e67ac700a108f786</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Akkadian Labs</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4166d709cbf2c503</t>
+          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>US-Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R1 RCM</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, HBase, Scala, Kafka, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,14 +1861,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5f27d8548d7b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1878,15 +1878,15 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Databricks Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Spokeo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Dataflow, Spark, PySpark, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67ac700a108f786</t>
+          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab350a33a1e5b663</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer / Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GreenStone Farm Credit Services</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>East Lansing, MI, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Scala, SQL Server, Kimball, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b5c77335a24de5c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Database Engineer (Information Systems Specialist 7)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Platform Engineer (Cloud Platform)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>SRE/DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
+          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Verity Transcend</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Machine Learning Test Capability Eng.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
+          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>Software Engineer, (L2) CDP</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - SRE</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6632f275b04054</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
+          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
+          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Verity Transcend</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Machine Learning Test Capability Eng.</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
+          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>GT Data Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
+          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Sr. Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>Applix Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,29 +3461,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
+          <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
+          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
+          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Cascadia Services</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
+          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>MTS Software Development Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>GT Data Engineer II</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
+          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Data &amp; Analytics Engineer</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Applix Inc.</t>
+          <t>ApolloMD</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
+          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Junior Backend Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Los Angeles Apparel</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,260 +3741,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer/Architect</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Cascadia Services</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Eagle, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>MTS Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Apply Digital</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Application Developer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>ApolloMD</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Junior Backend Developer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
         </is>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer I or II</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Dataflow</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432940e5c429b71c</t>
+          <t>https://www.indeed.com/viewjob?jk=9684b1e8c83efb55</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer I or II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Databricks, Medallion Architecture, BigQuery, Dataflow</t>
+          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94efcb73c0d62620</t>
+          <t>https://www.indeed.com/viewjob?jk=66a4800f2fbccdc3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer, Mortgage Servicing</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9684b1e8c83efb55</t>
+          <t>https://www.indeed.com/viewjob?jk=75c41866a1b74cb7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP Data Architect with 15 year's experience local to Chicago</t>
+          <t>Expert, Cloud Database Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sanford AI</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IAM, Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcb6ec77e71bc3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=3f3fe0d680994e3e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer + Gen AI (In-Person @ NYC)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Nucleusteq</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, RDS, Databricks, Spark</t>
+          <t>Glue, Google Cloud Platform, Dataflow, Cloud Storage, Hive, Spark, PySpark, Scala, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f631622e574168df</t>
+          <t>https://www.indeed.com/viewjob?jk=32f5af10a0a7af6f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - AWS Glue / Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66a4800f2fbccdc3</t>
+          <t>https://www.indeed.com/viewjob?jk=093ec4d8db7a7a45</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer, Mortgage Servicing</t>
+          <t>Senior Data Modeler</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Scala</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75c41866a1b74cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Expert, Cloud Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Moda Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, Databricks, Medallion Architecture, Scala, Snowflake, Oracle</t>
+          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f3fe0d680994e3e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8da5e0407b8df156</t>
+          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer + Gen AI (In-Person @ NYC)</t>
+          <t>Senior Engineer Core Infrastructure</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nucleusteq</t>
+          <t>JetBlue</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Glue, Google Cloud Platform, Dataflow, Cloud Storage, Hive, Spark, PySpark, Scala, MySQL, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32f5af10a0a7af6f</t>
+          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS Glue / Data Engineer</t>
+          <t>GCP Associate Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, SQS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=093ec4d8db7a7a45</t>
+          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Modeler</t>
+          <t>Engineer, Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ensemble Health Partners</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Blue Ash, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
         </is>
       </c>
     </row>
@@ -893,20 +893,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>National Council on Aging</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Sono Bello</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer Core Infrastructure</t>
+          <t>Senior GCP Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JetBlue</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
+          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GCP Associate Data Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,15 +1003,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
+          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer III</t>
+          <t>Senior GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Zone 5 Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, NoSQL, Tableau, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91905f991ae20797</t>
+          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Engineer, Data</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
+          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>National Council on Aging</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP API Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sono Bello</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
+          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
+          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior Data Engineer - AI and Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
+          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior GCP API Data Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
+          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>VERVE GROUP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
+          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Backend/AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Left Main REI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dragonfli Group LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51c0221c27e18ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI and Analytics</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Spokeo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, EMR, S3, RDS, Dataflow, Spark, PySpark, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
+          <t>https://www.indeed.com/viewjob?jk=e67ac700a108f786</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineering Consultant - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d70310be183ea2e</t>
+          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
+          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Remote / Contract)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
+          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure Databrick with Anaplan</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
+          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer - Databricks</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b0aa2be5209d6a</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
+          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
         </is>
       </c>
     </row>
@@ -1768,20 +1768,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Spokeo</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Dataflow, Spark, PySpark, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67ac700a108f786</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Akkadian Labs</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Scala, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e78fa05eac6e15</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure Databricks Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c94f00b22e57d86</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Database Engineer (Information Systems Specialist 7)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer (AWS &amp; Snowflake)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Verity Transcend</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Machine Learning Test Capability Eng.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
+          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
+          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud Platform)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,207 +2911,207 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e26c106f1b8164f</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Sr. Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Applix Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
+          <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SRE/DevOps Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64be9beb3d73dbb9</t>
+          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
+          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Cascadia Services</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
+          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>MTS Software Development Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Verity Transcend</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Test Capability Eng.</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer, (L2) CDP</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>ApolloMD</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, CI/CD, Kubernetes, Datadog</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,567 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ff081155f4529b</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Data Scientist I</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>HelioCampus</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Data Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Stanford Health Care</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Cloudelligent</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Cloudelligent</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Tiger Analytics</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58f2445240dbd78a</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>GT Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Data Modeling, ETL, ELT, Airflow, Apache Airflow, Python</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=057b8aa7c79e0b95</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Sr. Data &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Applix Inc.</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer/Architect</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Cascadia Services</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Eagle, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>MTS Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Apply Digital</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Application Developer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>ApolloMD</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Junior Backend Developer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Los Angeles Apparel</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cfd19ba4a3cf4a10</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -718,20 +718,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Moda Health</t>
+          <t>National Council on Aging</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Data Factory, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0980ce92de11d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Sono Bello</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5522b7c34600e8c9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer Core Infrastructure</t>
+          <t>Senior Data Engineer - AI and Analytics</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JetBlue</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Scala, DynamoDB, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35dc08cd58b4ac30</t>
+          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GCP Associate Data Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bridgewater, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bed49777ffc66e88</t>
+          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineer, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ensemble Health Partners</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Blue Ash, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Dataflow, Spark, Scala, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a968331cc3ce0086</t>
+          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend/AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>National Council on Aging</t>
+          <t>Left Main REI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
+          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sono Bello</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer</t>
+          <t>Azure Databrick with Anaplan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baad7a309761de2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Spokeo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, EMR, S3, RDS, Dataflow, Spark, PySpark, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f0fe94efdf94a50</t>
+          <t>https://www.indeed.com/viewjob?jk=e67ac700a108f786</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior GCP API Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67023c52c268b7ff</t>
+          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61a12b10547477fb</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8db06c11125fc14</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP API Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bc97caa06b5ca5</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57820fe41decd4fb</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI and Analytics</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Remote / Contract)</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VERVE GROUP</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fedc2cd59a8a631e</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Backend/AI Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Left Main REI</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Azure Databrick with Anaplan</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Data Modeling, MLOps</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d628829fcaf3036</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spokeo</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Dataflow, Spark, PySpark, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67ac700a108f786</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9f16501863249ef</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11bb6883564eae74</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d67068993909e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afd00ed67e04bb32</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9fbf2318173a6e1</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1191a515fb7b159c</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer (Information Systems Specialist 7)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Department of Human Services</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Salem, OR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Verity Transcend</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Machine Learning Test Capability Eng.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Cloudelligent</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,207 +2176,207 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Sr. Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Applix Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Cascadia Services</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>MTS Software Development Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,777 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Senior AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Scribd, Inc.</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Department of Human Services</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Salem, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Data Engineer (AWS &amp; Snowflake)</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, RDS, Scala, Snowflake, ETL, dbt, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ed1f30d22131d</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Lakeview Loan Servicing</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Backend Engineer (SF/On-site)</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Soulside AI</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>FFF Enterprises</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Temecula, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Keysight Technologies</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Data Visualization Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Verity Transcend</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Machine Learning Test Capability Eng.</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Nokia</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Data Scientist I</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>HelioCampus</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Data Quality Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Stanford Health Care</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Cloudelligent</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Cloudelligent</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Sr. Data &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Applix Inc.</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer/Architect</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Cascadia Services</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Eagle, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>MTS Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Apply Digital</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Application Developer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>ApolloMD</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5425897f4c974bab</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-09.xlsx
+++ b/results/job_matches_2026-05-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Modeler</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>National Council on Aging</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a7c1ce37c241a5</t>
+          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>National Council on Aging</t>
+          <t>Sono Bello</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Scala, SQL Server, DynamoDB, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ecdb3ec5b7a62d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - AI and Analytics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sono Bello</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Buffalo Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Spark, PySpark, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca29527e5a6209f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - AI and Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Buffalo Grove, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Spark, Spark Streaming, Kafka, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e849cada055fab1d</t>
+          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Backend/AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Left Main REI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58fe1722e4dbca11</t>
+          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f44f93d98783e436</t>
+          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Backend/AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Left Main REI</t>
+          <t>Spokeo</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pasadena, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, IAM, Scala, Snowflake</t>
+          <t>AWS, EMR, S3, RDS, Dataflow, Spark, PySpark, Scala, DynamoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eaa1cbe99589993</t>
+          <t>https://www.indeed.com/viewjob?jk=e67ac700a108f786</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>NorthMarq</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cde0addac86462a</t>
+          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azure Databrick with Anaplan</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae17f8ab37624a34</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spokeo</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pasadena, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Dataflow, Spark, PySpark, Scala, DynamoDB, Data Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67ac700a108f786</t>
+          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NorthMarq</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eacdba745833a36d</t>
+          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8000eeb7bf0b7</t>
+          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ccb2dafd80220</t>
+          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1699c5e5a52cf65b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f4496eb848e1f99</t>
+          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=962d25633e74669c</t>
+          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc837d75c1dcb1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3ed6e6205dc1a0b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=013fffe990604733</t>
+          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c48fd471a487a9</t>
+          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce1e0197ece7de38</t>
+          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13a8a9ffe0e9c11b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=018b5c229969e4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999d8b3439b32a12</t>
+          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2fc56181cec43b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b279a521ced8b701</t>
+          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a9449b2860b07b</t>
+          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee06e813bf9443d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Lakeview Loan Servicing</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,19 +1686,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010c2a63cf43d2c1</t>
+          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Backend Engineer (SF/On-site)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Soulside AI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372968a57be9635c</t>
+          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior AI Data Engineer</t>
+          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Spark, Data Modeling, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a56fcdd8beeec5b</t>
+          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Database Engineer (Information Systems Specialist 7)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Department of Human Services</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salem, OR, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4569b261734dc20c</t>
+          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Machine Learning Test Capability Eng.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, Data Modeling</t>
+          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98900424ffd4451b</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Backend Engineer (SF/On-site)</t>
+          <t>Data Scientist I</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Soulside AI</t>
+          <t>HelioCampus</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, ECS, RDS, Azure, GCP, Spark, Scala, Kafka</t>
+          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94ee2e4b06fb2c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Analyst, Business Data Platform &amp; Analytics</t>
+          <t>Senior Data Quality Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Stanford Health Care</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,94 +1896,94 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5ea9f2fc1468665</t>
+          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr. Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Applix Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, Oracle, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac992d12306d7243</t>
+          <t>https://www.indeed.com/viewjob?jk=a4b72b71f93e9340</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>Sr. Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Verity Transcend</t>
+          <t>Applix Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Snowflake, Data Modeling, Snowflake Schema, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1731d4f83dcc698</t>
+          <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine Learning Test Capability Eng.</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Photon, Spark, Scala, MySQL, Azure DevOps, Bitbucket, Python, SQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85e9be561e29b0</t>
+          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HelioCampus</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, S3, RDS, Power BI, Tableau, MLOps, MLflow, Docker, Airflow, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40710e09e7c21122</t>
+          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Quality Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Stanford Health Care</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Data Modeling, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d411e0319cb3614a</t>
+          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>Senior Data Engineer/Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>Cascadia Services</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Eagle, ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,29 +2096,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606de80ba3576b50</t>
+          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. AWS DevOps Engineer- Kubernetes Expertise</t>
+          <t>MTS Software Development Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cloudelligent</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=600823f79b18dde8</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior DevOps Engineer (Talent Pipeline)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Apply Digital</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2175,251 +2175,6 @@
         </is>
       </c>
       <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e80faca856a314</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Sr. Data &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Applix Inc.</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Scala, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76cfbc9e7b83be2f</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bcd0330cb00d0d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68fed7c70121eb1d</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=04d5028d2b83e4a1</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer/Architect</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Cascadia Services</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Eagle, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, SQL Server, Data Modeling, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a14387759e6fa434</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MTS Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Data Lake Storage, Unity Catalog, Scala, Data Modeling, ETL, ELT, Python</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b1530a49d3281</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer (Talent Pipeline)</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Apply Digital</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>AR, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3b57708f8d3c4737</t>
         </is>
